--- a/data/industry/CFM/uMCP.xlsx
+++ b/data/industry/CFM/uMCP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6347CC9-B0F8-4797-B362-0FAD485840E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E65129-7202-452E-9970-60FB235A1490}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="666" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1099,7 +1099,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1112,6 +1112,121 @@
       </c>
       <c r="G28" s="12">
         <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F29" s="12">
+        <v>76.2</v>
+      </c>
+      <c r="G29" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F30" s="12">
+        <v>76.2</v>
+      </c>
+      <c r="G30" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F31" s="12">
+        <v>76.2</v>
+      </c>
+      <c r="G31" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>89.1</v>
+      </c>
+      <c r="F32" s="12">
+        <v>92.2</v>
+      </c>
+      <c r="G32" s="12">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>89.1</v>
+      </c>
+      <c r="F33" s="12">
+        <v>92.2</v>
+      </c>
+      <c r="G33" s="12">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1122,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1763,7 +1878,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1776,6 +1891,121 @@
       </c>
       <c r="G28" s="9">
         <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9">
+        <v>88.5</v>
+      </c>
+      <c r="F29" s="9">
+        <v>92</v>
+      </c>
+      <c r="G29" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="9">
+        <v>88.5</v>
+      </c>
+      <c r="F30" s="9">
+        <v>92</v>
+      </c>
+      <c r="G30" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="9">
+        <v>88.5</v>
+      </c>
+      <c r="F31" s="9">
+        <v>92</v>
+      </c>
+      <c r="G31" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="9">
+        <v>101.5</v>
+      </c>
+      <c r="F32" s="9">
+        <v>105</v>
+      </c>
+      <c r="G32" s="9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="9">
+        <v>101.5</v>
+      </c>
+      <c r="F33" s="9">
+        <v>105</v>
+      </c>
+      <c r="G33" s="9">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1786,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -2427,7 +2657,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -2440,6 +2670,121 @@
       </c>
       <c r="G28" s="14">
         <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>102</v>
+      </c>
+      <c r="F29" s="14">
+        <v>108</v>
+      </c>
+      <c r="G29" s="14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>102</v>
+      </c>
+      <c r="F30" s="14">
+        <v>108</v>
+      </c>
+      <c r="G30" s="14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>102</v>
+      </c>
+      <c r="F31" s="14">
+        <v>108</v>
+      </c>
+      <c r="G31" s="14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>126</v>
+      </c>
+      <c r="G32" s="14">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>126</v>
+      </c>
+      <c r="G33" s="14">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2450,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3092,7 +3437,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -3105,6 +3450,121 @@
       </c>
       <c r="G28" s="14">
         <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>126</v>
+      </c>
+      <c r="F29" s="14">
+        <v>129.5</v>
+      </c>
+      <c r="G29" s="14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>126</v>
+      </c>
+      <c r="F30" s="14">
+        <v>129.5</v>
+      </c>
+      <c r="G30" s="14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>126</v>
+      </c>
+      <c r="F31" s="14">
+        <v>129.5</v>
+      </c>
+      <c r="G31" s="14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>149</v>
+      </c>
+      <c r="F32" s="14">
+        <v>152.5</v>
+      </c>
+      <c r="G32" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>149</v>
+      </c>
+      <c r="F33" s="14">
+        <v>152.5</v>
+      </c>
+      <c r="G33" s="14">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/uMCP.xlsx
+++ b/data/industry/CFM/uMCP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E20242-F079-4B8B-835C-100036285C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FD053F-0C88-43A9-9FEE-AD14EC4E27A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="uMCP(LPDDR4X + UFS2.2)4GB+128GB" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -70,25 +70,25 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -101,7 +101,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,50 +132,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -458,19 +458,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -516,7 +516,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -539,7 +539,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -562,7 +562,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -585,7 +585,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -608,7 +608,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -631,7 +631,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -654,7 +654,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -677,7 +677,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -700,7 +700,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -723,7 +723,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -746,7 +746,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -769,7 +769,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -792,7 +792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -815,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -861,7 +861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -884,7 +884,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -907,7 +907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -930,7 +930,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -953,7 +953,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -976,7 +976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -999,7 +999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1365,6 +1365,144 @@
       </c>
       <c r="G39" s="12">
         <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F40" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G40" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>87.1</v>
+      </c>
+      <c r="F41" s="12">
+        <v>90.2</v>
+      </c>
+      <c r="G41" s="12">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>87.1</v>
+      </c>
+      <c r="F42" s="12">
+        <v>90.2</v>
+      </c>
+      <c r="G42" s="12">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>86.1</v>
+      </c>
+      <c r="F43" s="12">
+        <v>89.2</v>
+      </c>
+      <c r="G43" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>86.1</v>
+      </c>
+      <c r="F44" s="12">
+        <v>89.2</v>
+      </c>
+      <c r="G44" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>86.1</v>
+      </c>
+      <c r="F45" s="12">
+        <v>89.2</v>
+      </c>
+      <c r="G45" s="12">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1375,19 +1513,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1410,7 +1548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1433,7 +1571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1456,7 +1594,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1479,7 +1617,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1502,7 +1640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1525,7 +1663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1548,7 +1686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1571,7 +1709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1594,7 +1732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1617,7 +1755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1640,7 +1778,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1663,7 +1801,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1686,7 +1824,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1709,7 +1847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1732,7 +1870,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1755,7 +1893,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1778,7 +1916,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1801,7 +1939,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -1824,7 +1962,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -1847,7 +1985,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -1870,7 +2008,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -1893,7 +2031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1916,7 +2054,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1939,7 +2077,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1962,7 +2100,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1985,7 +2123,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2008,7 +2146,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2031,7 +2169,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2054,7 +2192,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2077,7 +2215,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2100,7 +2238,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2123,7 +2261,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2146,7 +2284,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2169,7 +2307,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2192,7 +2330,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2215,7 +2353,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2238,7 +2376,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2261,7 +2399,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2282,6 +2420,144 @@
       </c>
       <c r="G39" s="9">
         <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F40" s="9">
+        <v>114</v>
+      </c>
+      <c r="G40" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>107.5</v>
+      </c>
+      <c r="F41" s="9">
+        <v>111</v>
+      </c>
+      <c r="G41" s="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="9">
+        <v>107.5</v>
+      </c>
+      <c r="F42" s="9">
+        <v>111</v>
+      </c>
+      <c r="G42" s="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="9">
+        <v>105.5</v>
+      </c>
+      <c r="F43" s="9">
+        <v>109</v>
+      </c>
+      <c r="G43" s="9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="9">
+        <v>105.5</v>
+      </c>
+      <c r="F44" s="9">
+        <v>109</v>
+      </c>
+      <c r="G44" s="9">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="9">
+        <v>105.5</v>
+      </c>
+      <c r="F45" s="9">
+        <v>109</v>
+      </c>
+      <c r="G45" s="9">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2292,19 +2568,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2327,7 +2603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2350,7 +2626,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2373,7 +2649,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2396,7 +2672,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2419,7 +2695,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2442,7 +2718,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2465,7 +2741,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2488,7 +2764,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2511,7 +2787,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2534,7 +2810,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2557,7 +2833,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2580,7 +2856,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2603,7 +2879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2626,7 +2902,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2649,7 +2925,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2672,7 +2948,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2695,7 +2971,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2718,7 +2994,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2741,7 +3017,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2764,7 +3040,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2787,7 +3063,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2810,7 +3086,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2833,7 +3109,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2856,7 +3132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2879,7 +3155,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2902,7 +3178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2925,7 +3201,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2948,7 +3224,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2971,7 +3247,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2994,7 +3270,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3017,7 +3293,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3040,7 +3316,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3063,7 +3339,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3086,7 +3362,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3109,7 +3385,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3132,7 +3408,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3155,7 +3431,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3178,7 +3454,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3199,6 +3475,144 @@
       </c>
       <c r="G39" s="14">
         <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>133</v>
+      </c>
+      <c r="F40" s="14">
+        <v>139</v>
+      </c>
+      <c r="G40" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>130</v>
+      </c>
+      <c r="F41" s="14">
+        <v>136</v>
+      </c>
+      <c r="G41" s="14">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>130</v>
+      </c>
+      <c r="F42" s="14">
+        <v>136</v>
+      </c>
+      <c r="G42" s="14">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>130</v>
+      </c>
+      <c r="F43" s="14">
+        <v>136</v>
+      </c>
+      <c r="G43" s="14">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>130</v>
+      </c>
+      <c r="F44" s="14">
+        <v>136</v>
+      </c>
+      <c r="G44" s="14">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>130</v>
+      </c>
+      <c r="F45" s="14">
+        <v>136</v>
+      </c>
+      <c r="G45" s="14">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3209,20 +3623,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="14"/>
+    <col min="6" max="6" width="9.5546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="15"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3245,7 +3660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3268,7 +3683,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3291,7 +3706,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3314,7 +3729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3337,7 +3752,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3360,7 +3775,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3383,7 +3798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3406,7 +3821,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3429,7 +3844,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3452,7 +3867,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3475,7 +3890,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3498,7 +3913,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3521,7 +3936,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3544,7 +3959,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3567,7 +3982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3590,7 +4005,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3613,7 +4028,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3636,7 +4051,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3659,7 +4074,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3682,7 +4097,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3705,7 +4120,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3728,7 +4143,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3751,7 +4166,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3774,7 +4189,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3797,7 +4212,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3820,7 +4235,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3843,7 +4258,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3866,7 +4281,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3889,7 +4304,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3912,7 +4327,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3935,7 +4350,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3958,7 +4373,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3981,7 +4396,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4004,7 +4419,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4027,7 +4442,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4050,7 +4465,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4073,7 +4488,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4096,7 +4511,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4117,6 +4532,144 @@
       </c>
       <c r="G39" s="14">
         <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>162</v>
+      </c>
+      <c r="F40" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G40" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>159</v>
+      </c>
+      <c r="F41" s="14">
+        <v>162.5</v>
+      </c>
+      <c r="G41" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>159</v>
+      </c>
+      <c r="F42" s="14">
+        <v>162.5</v>
+      </c>
+      <c r="G42" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>159</v>
+      </c>
+      <c r="F43" s="14">
+        <v>162.5</v>
+      </c>
+      <c r="G43" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>159</v>
+      </c>
+      <c r="F44" s="14">
+        <v>162.5</v>
+      </c>
+      <c r="G44" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>159</v>
+      </c>
+      <c r="F45" s="14">
+        <v>162.5</v>
+      </c>
+      <c r="G45" s="14">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
